--- a/out/bbb.xlsx
+++ b/out/bbb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9293C4BE-C0D9-4A26-B579-A4247CD7F679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50426A20-CE20-4241-8911-4D87D193D9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6470" yWindow="1220" windowWidth="19040" windowHeight="12700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="23840" windowHeight="12700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/out/bbb.xlsx
+++ b/out/bbb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50426A20-CE20-4241-8911-4D87D193D9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{051CE0F6-72CA-4106-98B4-1338A1FDAFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="720" yWindow="720" windowWidth="23840" windowHeight="12700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
